--- a/samples/sample.xlsx
+++ b/samples/sample.xlsx
@@ -169,7 +169,7 @@
     <t>[![License: MIT](https://img.shields.io/badge/License-MIT-blue.svg)](https://opensource.org/licenses/MIT)</t>
   </si>
   <si>
-    <t>[![GitHub](https://img.shields.io/github/stars/NAOHIDEOTA/documelt?style=social)](https://github.com/NAOHIDEOTA/documelt)</t>
+    <t>[![GitHub](https://img.shields.io/github/stars/naohidden/documelt?style=social)](https://github.com/naohidden/documelt)</t>
   </si>
   <si>
     <t>**Rust + WebAssembly** によるブラウザ向けドキュメントテキスト抽出ライブラリ。</t>
@@ -394,10 +394,10 @@
     <t>- **ファイルサイズ** — ブラウザメモリに制約あり。10MB 以下を推奨</t>
   </si>
   <si>
-    <t>[GitHub Issues](https://github.com/NAOHIDEOTA/documelt/issues) でバグ報告・機能リクエストを受け付けています。</t>
-  </si>
-  <si>
-    <t>[MIT](LICENSE) - Copyright (c) 2026 NAOHIDEOTA</t>
+    <t>[GitHub Issues](https://github.com/naohidden/documelt/issues) でバグ報告・機能リクエストを受け付けています。</t>
+  </si>
+  <si>
+    <t>[MIT](LICENSE) - Copyright (c) 2026 naohidden</t>
   </si>
   <si>
     <t># documelt</t>
